--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>92986</v>
+        <v>92988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>92988</v>
+        <v>92990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>92990</v>
+        <v>92991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>92991</v>
+        <v>92997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>92997</v>
+        <v>93001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>93001</v>
+        <v>93003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>93003</v>
+        <v>93016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136921046</v>
       </c>
       <c r="B9" t="n">
-        <v>58171</v>
+        <v>58184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136921031</v>
       </c>
       <c r="B10" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>93016</v>
+        <v>93018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>136921035</v>
       </c>
       <c r="B7" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136921046</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>136921031</v>
       </c>
       <c r="B10" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136921024</v>
       </c>
       <c r="B11" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921027</v>
       </c>
       <c r="B5" t="n">
-        <v>93018</v>
+        <v>93021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>136921044</v>
       </c>
       <c r="B6" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89355</v>
+        <v>89365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,48 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136921027</v>
+        <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>93021</v>
+        <v>83504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5371</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtätskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Peniophora septentrionalis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Laurila</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogarna mellan E10 och Drottninghällan, SO om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758932</v>
+        <v>759045</v>
       </c>
       <c r="R5" t="n">
-        <v>7513388</v>
+        <v>7513294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,24 +1074,18 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Väldigt mycket gissning, ska samlas in och utredas vidare</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog med lövinslag på blåbärsris</t>
+          <t>Medelåldrig barrblandskog med lövinslag på blåbärsris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1111,16 +1102,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921027</t>
+          <t>https://artportalen.se/Sighting/136921044</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136921044</v>
+        <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>83494</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759045</v>
+        <v>758966</v>
       </c>
       <c r="R6" t="n">
-        <v>7513294</v>
+        <v>7513080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,16 +1209,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921044</t>
+          <t>https://artportalen.se/Sighting/136921035</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136921035</v>
+        <v>136921039</v>
       </c>
       <c r="B7" t="n">
-        <v>80122</v>
+        <v>5504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skogarna mellan E10 och Drottninghällan, SO om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758966</v>
+        <v>758773</v>
       </c>
       <c r="R7" t="n">
-        <v>7513080</v>
+        <v>7513149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,6 +1299,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,16 +1322,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921035</t>
+          <t>https://artportalen.se/Sighting/136921039</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136921039</v>
+        <v>136921046</v>
       </c>
       <c r="B8" t="n">
-        <v>5498</v>
+        <v>58196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,39 +1339,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>103022</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skogarna mellan E10 och Drottninghällan, SO om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758773</v>
+        <v>758853</v>
       </c>
       <c r="R8" t="n">
-        <v>7513149</v>
+        <v>7513217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,13 +1407,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Medelåldrig barrblandskog med lövinslag på blåbärsris</t>
+          <t>Äldre barrblandskog med lövinslag på blåbärsris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1438,16 +1429,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921039</t>
+          <t>https://artportalen.se/Sighting/136921046</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136921046</v>
+        <v>136921031</v>
       </c>
       <c r="B9" t="n">
-        <v>58186</v>
+        <v>58137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103022</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758853</v>
+        <v>758941</v>
       </c>
       <c r="R9" t="n">
-        <v>7513217</v>
+        <v>7513323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,16 +1536,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136921046</t>
+          <t>https://artportalen.se/Sighting/136921031</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136921031</v>
+        <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>58127</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>260591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758941</v>
+        <v>759011</v>
       </c>
       <c r="R10" t="n">
-        <v>7513323</v>
+        <v>7513304</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1626,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog med lövinslag på blåbärsris</t>
+          <t>Medelåldrig barrblandskog med lövinslag på blåbärsris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1651,113 +1642,6 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136921031</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>136921024</v>
-      </c>
-      <c r="B11" t="n">
-        <v>79526</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Skogarna mellan E10 och Drottninghällan, SO om Svappavaara, T lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>759011</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7513304</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Medelåldrig barrblandskog med lövinslag på blåbärsris</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136921024</t>
         </is>
@@ -1774,7 +1658,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89365</v>
+        <v>89366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89366</v>
+        <v>89369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136921046</v>
       </c>
       <c r="B8" t="n">
-        <v>58196</v>
+        <v>58197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>136921031</v>
       </c>
       <c r="B9" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89369</v>
+        <v>89374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136921046</v>
       </c>
       <c r="B8" t="n">
-        <v>58197</v>
+        <v>58198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>136921031</v>
       </c>
       <c r="B9" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89374</v>
+        <v>89385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89385</v>
+        <v>89386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29048-2026 artfynd.xlsx
+++ b/artfynd/A 29048-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136921028</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136921030</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136921042</v>
       </c>
       <c r="B4" t="n">
-        <v>89386</v>
+        <v>89389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136921044</v>
       </c>
       <c r="B5" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136921035</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136921024</v>
       </c>
       <c r="B10" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
